--- a/templates/report.xlsx
+++ b/templates/report.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr date1904="1" showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\justi\GitHub\WRF_Analysis\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD7632-33CF-455D-99E1-2B930DC477E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41EA9A69-DDC0-43ED-98DA-08F515CB57FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="C595" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="2910" yWindow="-17355" windowWidth="14340" windowHeight="8145" tabRatio="915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="14400" windowHeight="8170" tabRatio="915"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="7" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="179">
   <si>
     <t>Instrument</t>
   </si>
@@ -603,9 +603,6 @@
     <t>integer</t>
   </si>
   <si>
-    <t>percent</t>
-  </si>
-  <si>
     <t>RHOR_AT_SHOCK</t>
   </si>
   <si>
@@ -628,21 +625,18 @@
   </si>
   <si>
     <t>090-124</t>
-  </si>
-  <si>
-    <t>N230207-001-999</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.000E+00"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.000"/>
+    <numFmt numFmtId="175" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -965,7 +959,7 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -978,7 +972,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -1002,7 +996,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1024,7 +1018,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1084,11 +1078,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="174" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="175" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -1111,11 +1105,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -1140,7 +1134,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFill="1"/>
@@ -1154,7 +1148,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1216,10 +1210,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Comma 2" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="3"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -1680,27 +1674,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.3046875" style="45" customWidth="1"/>
+    <col min="1" max="1" width="30.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.3828125" style="45" customWidth="1"/>
     <col min="3" max="3" width="9.4609375" style="45" customWidth="1"/>
     <col min="4" max="4" width="8.15234375" style="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.69140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.61328125" style="45" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.84375" style="45" customWidth="1"/>
-    <col min="7" max="7" width="9.3046875" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.3828125" style="45" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="53" style="45" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.69140625" style="45" customWidth="1"/>
+    <col min="9" max="9" width="16.61328125" style="45" customWidth="1"/>
     <col min="10" max="10" width="14.15234375" style="45" customWidth="1"/>
-    <col min="11" max="11" width="17.69140625" style="45" customWidth="1"/>
+    <col min="11" max="11" width="17.61328125" style="45" customWidth="1"/>
     <col min="12" max="12" width="17.15234375" style="45" customWidth="1"/>
     <col min="13" max="15" width="14.15234375" style="45" customWidth="1"/>
-    <col min="16" max="17" width="24.69140625" style="45" customWidth="1"/>
+    <col min="16" max="17" width="24.61328125" style="45" customWidth="1"/>
     <col min="18" max="18" width="39" style="45" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="45"/>
+    <col min="19" max="16384" width="11" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1718,12 +1712,10 @@
       <c r="A2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="42" t="s">
-        <v>180</v>
-      </c>
+      <c r="B2" s="42"/>
       <c r="C2" s="47" t="b">
         <f>AND(LEN(SHOT_ID)=15,ISTEXT(LEFT(SHOT_ID,1))=TRUE,MID(SHOT_ID,8,1)="-",ISNUMBER(VALUE(MID(SHOT_ID,2,6))),MID(SHOT_ID,12,1)="-",ISNUMBER(VALUE(MID(SHOT_ID,9,3))),ISNUMBER(VALUE(MID(SHOT_ID,13,3))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>42</v>
@@ -1733,12 +1725,10 @@
       <c r="A3" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="42" t="s">
-        <v>49</v>
-      </c>
+      <c r="B3" s="42"/>
       <c r="C3" s="49" t="b">
         <f>AND(NOT(ISBLANK(B3)),NOT(ISNA(VLOOKUP(Port,Ports,1,FALSE)=Port)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>43</v>
@@ -2573,6 +2563,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection password="C595" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B6:G6"/>
   </mergeCells>
@@ -2611,17 +2602,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D43:F47 D33:F37 D23:F27 D13:F17 D54:F58" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D43:F47 D33:F37 D23:F27 D13:F17 D54:F58">
       <formula1>-1000000000000000</formula1>
       <formula2>1000000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Must choose a valid port" promptTitle="Choosea port from the valid list" sqref="B3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Must choose a valid port" promptTitle="Choosea port from the valid list" sqref="B3">
       <formula1>Ports</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
       <formula1>QualityList</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D41:F42 D11:F12 D21:F22 D31:F32 D52:F53" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D41:F42 D11:F12 D21:F22 D31:F32 D52:F53">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -2632,7 +2623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -2674,7 +2665,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B4" s="17"/>
     </row>
@@ -2707,20 +2698,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.15234375" customWidth="1"/>
     <col min="2" max="2" width="25.15234375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="41.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.61328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.15234375" customWidth="1"/>
-    <col min="5" max="5" width="14.69140625" customWidth="1"/>
+    <col min="5" max="5" width="14.61328125" customWidth="1"/>
     <col min="6" max="6" width="16.4609375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.69140625" customWidth="1"/>
+    <col min="7" max="7" width="9.61328125" customWidth="1"/>
     <col min="8" max="9" width="8.84375" customWidth="1"/>
-    <col min="10" max="10" width="15.69140625" customWidth="1"/>
+    <col min="10" max="10" width="15.61328125" customWidth="1"/>
     <col min="11" max="11" width="12.84375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2729,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="41" t="s">
@@ -2741,7 +2732,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="28" t="s">
@@ -2808,7 +2799,7 @@
       </c>
       <c r="B7" s="9" t="str">
         <f ca="1">TRIM(UPPER(INDIRECT("SHOT_ID")))</f>
-        <v>N230207-001-999</v>
+        <v/>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2829,7 +2820,7 @@
       </c>
       <c r="B8" s="10" t="str">
         <f ca="1">CONCATENATE(SUBSYSTEM_KEY,"|TC",INDIRECT("Port"),"|",INDIRECT("Instrument"),"|ANALYSIS|SHOT|SUMMARY")</f>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|SHOT|SUMMARY</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|SHOT|SUMMARY</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -3203,37 +3194,37 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.69140625" style="79" customWidth="1"/>
-    <col min="2" max="2" width="62.69140625" style="118" customWidth="1"/>
+    <col min="1" max="1" width="11.61328125" style="79" customWidth="1"/>
+    <col min="2" max="2" width="62.61328125" style="118" customWidth="1"/>
     <col min="3" max="3" width="46.4609375" style="118" customWidth="1"/>
     <col min="4" max="4" width="36.15234375" style="79" customWidth="1"/>
     <col min="5" max="5" width="83.15234375" style="79" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.69140625" style="79" customWidth="1"/>
+    <col min="6" max="6" width="17.61328125" style="79" customWidth="1"/>
     <col min="7" max="7" width="14.15234375" style="79" customWidth="1"/>
-    <col min="8" max="8" width="15.3046875" style="79" customWidth="1"/>
-    <col min="9" max="9" width="16.3046875" style="79" customWidth="1"/>
+    <col min="8" max="8" width="15.3828125" style="79" customWidth="1"/>
+    <col min="9" max="9" width="16.3828125" style="79" customWidth="1"/>
     <col min="10" max="10" width="12.15234375" style="79" customWidth="1"/>
     <col min="11" max="12" width="17.15234375" style="79" customWidth="1"/>
-    <col min="13" max="13" width="18.69140625" style="79" customWidth="1"/>
-    <col min="14" max="14" width="17.69140625" style="79" customWidth="1"/>
-    <col min="15" max="15" width="19.69140625" style="79" customWidth="1"/>
+    <col min="13" max="13" width="18.61328125" style="79" customWidth="1"/>
+    <col min="14" max="14" width="17.61328125" style="79" customWidth="1"/>
+    <col min="15" max="15" width="19.61328125" style="79" customWidth="1"/>
     <col min="16" max="16" width="19.15234375" style="79" customWidth="1"/>
     <col min="17" max="17" width="14" style="79" customWidth="1"/>
-    <col min="18" max="18" width="14.69140625" style="79" customWidth="1"/>
+    <col min="18" max="18" width="14.61328125" style="79" customWidth="1"/>
     <col min="19" max="19" width="31.84375" style="79" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.84375" style="79" customWidth="1"/>
-    <col min="21" max="21" width="8.69140625" style="79" customWidth="1"/>
-    <col min="22" max="22" width="4.69140625" style="79" customWidth="1"/>
+    <col min="21" max="21" width="8.61328125" style="79" customWidth="1"/>
+    <col min="22" max="22" width="4.61328125" style="79" customWidth="1"/>
     <col min="23" max="23" width="13.15234375" style="79" customWidth="1"/>
     <col min="24" max="24" width="7" style="79" customWidth="1"/>
     <col min="25" max="25" width="10.15234375" style="79" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9" style="79"/>
-    <col min="27" max="27" width="28.3046875" style="79" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="79"/>
+    <col min="26" max="26" width="11" style="79" customWidth="1"/>
+    <col min="27" max="27" width="28.3828125" style="79" customWidth="1"/>
+    <col min="28" max="16384" width="11" style="79"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
@@ -3371,7 +3362,7 @@
       </c>
       <c r="B6" s="94" t="str">
         <f ca="1">TRIM(UPPER(INDIRECT("SHOT_ID")))</f>
-        <v>N230207-001-999</v>
+        <v/>
       </c>
       <c r="C6" s="94"/>
       <c r="D6" s="81"/>
@@ -3632,7 +3623,7 @@
       </c>
       <c r="B12" s="97" t="str">
         <f t="shared" ref="B12:B18" ca="1" si="0">CONCATENATE(SUBSYSTEM_KEY,"|TC",INDIRECT("Port"),"|",INDIRECT("Instrument"),"|ANALYSIS|UPPER_LEFT|", C12)</f>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|SHOCK_D3HE_P_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|SHOCK_D3HE_P_YIELD</v>
       </c>
       <c r="C12" s="97" t="s">
         <v>73</v>
@@ -3727,10 +3718,10 @@
       </c>
       <c r="B13" s="97" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|COMPRESSION_D3HEP_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|COMPRESSION_D3HEP_YIELD</v>
       </c>
       <c r="C13" s="97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D13" s="104" t="str">
         <f t="shared" ref="D13:D45" ca="1" si="6">IF(ISBLANK(OFFSET(INDIRECT(R13), 0, -1, 1, 1)), "", OFFSET(INDIRECT(R13), 0, -1, 1, 1))</f>
@@ -3822,10 +3813,10 @@
       </c>
       <c r="B14" s="97" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|RHOR_AT_SHOCK</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|RHOR_AT_SHOCK</v>
       </c>
       <c r="C14" s="97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D14" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -3917,10 +3908,10 @@
       </c>
       <c r="B15" s="97" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|RHOR_AT_COMPRESSION</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|RHOR_AT_COMPRESSION</v>
       </c>
       <c r="C15" s="97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D15" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4012,10 +4003,10 @@
       </c>
       <c r="B16" s="97" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|KO_P_TO_NEUTRON_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|KO_P_TO_NEUTRON_RATIO</v>
       </c>
       <c r="C16" s="97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D16" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4107,10 +4098,10 @@
       </c>
       <c r="B17" s="97" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
       </c>
       <c r="C17" s="97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D17" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4202,10 +4193,10 @@
       </c>
       <c r="B18" s="97" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
       </c>
       <c r="C18" s="97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D18" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4297,7 +4288,7 @@
       </c>
       <c r="B19" s="97" t="str">
         <f t="shared" ref="B19:B25" ca="1" si="19">CONCATENATE(SUBSYSTEM_KEY,"|TC",INDIRECT("Port"),"|",INDIRECT("Instrument"),"|ANALYSIS|UPPER_RIGHT|", C19)</f>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|SHOCK_D3HE_P_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|SHOCK_D3HE_P_YIELD</v>
       </c>
       <c r="C19" s="97" t="s">
         <v>73</v>
@@ -4392,10 +4383,10 @@
       </c>
       <c r="B20" s="97" t="str">
         <f t="shared" ca="1" si="19"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|COMPRESSION_D3HEP_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|COMPRESSION_D3HEP_YIELD</v>
       </c>
       <c r="C20" s="97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D20" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4487,10 +4478,10 @@
       </c>
       <c r="B21" s="97" t="str">
         <f t="shared" ca="1" si="19"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|RHOR_AT_SHOCK</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|RHOR_AT_SHOCK</v>
       </c>
       <c r="C21" s="97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D21" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4582,10 +4573,10 @@
       </c>
       <c r="B22" s="97" t="str">
         <f t="shared" ca="1" si="19"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|RHOR_AT_COMPRESSION</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|RHOR_AT_COMPRESSION</v>
       </c>
       <c r="C22" s="97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D22" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4677,10 +4668,10 @@
       </c>
       <c r="B23" s="97" t="str">
         <f t="shared" ca="1" si="19"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|KO_P_TO_NEUTRON_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|KO_P_TO_NEUTRON_RATIO</v>
       </c>
       <c r="C23" s="97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D23" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4772,10 +4763,10 @@
       </c>
       <c r="B24" s="97" t="str">
         <f t="shared" ca="1" si="19"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
       </c>
       <c r="C24" s="97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D24" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4867,10 +4858,10 @@
       </c>
       <c r="B25" s="97" t="str">
         <f t="shared" ca="1" si="19"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|UPPER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|UPPER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
       </c>
       <c r="C25" s="97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D25" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4962,7 +4953,7 @@
       </c>
       <c r="B26" s="97" t="str">
         <f t="shared" ref="B26:B32" ca="1" si="20">CONCATENATE(SUBSYSTEM_KEY,"|TC",INDIRECT("Port"),"|",INDIRECT("Instrument"),"|ANALYSIS|LOWER_LEFT|", C26)</f>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|SHOCK_D3HE_P_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|SHOCK_D3HE_P_YIELD</v>
       </c>
       <c r="C26" s="97" t="s">
         <v>73</v>
@@ -5019,7 +5010,7 @@
         <v/>
       </c>
       <c r="Q26" s="81" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="R26" s="109" t="s">
         <v>110</v>
@@ -5056,10 +5047,10 @@
       </c>
       <c r="B27" s="97" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|COMPRESSION_D3HEP_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|COMPRESSION_D3HEP_YIELD</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D27" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5151,10 +5142,10 @@
       </c>
       <c r="B28" s="97" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|RHOR_AT_SHOCK</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|RHOR_AT_SHOCK</v>
       </c>
       <c r="C28" s="97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5246,10 +5237,10 @@
       </c>
       <c r="B29" s="97" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|RHOR_AT_COMPRESSION</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|RHOR_AT_COMPRESSION</v>
       </c>
       <c r="C29" s="97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D29" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5341,10 +5332,10 @@
       </c>
       <c r="B30" s="97" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|KO_P_TO_NEUTRON_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|KO_P_TO_NEUTRON_RATIO</v>
       </c>
       <c r="C30" s="97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D30" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5436,10 +5427,10 @@
       </c>
       <c r="B31" s="97" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
       </c>
       <c r="C31" s="97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D31" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5531,10 +5522,10 @@
       </c>
       <c r="B32" s="97" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_LEFT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
       </c>
       <c r="C32" s="97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D32" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5626,7 +5617,7 @@
       </c>
       <c r="B33" s="97" t="str">
         <f t="shared" ref="B33:B39" ca="1" si="21">CONCATENATE(SUBSYSTEM_KEY,"|TC",INDIRECT("Port"),"|",INDIRECT("Instrument"),"|ANALYSIS|LOWER_RIGHT|", C33)</f>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|SHOCK_D3HE_P_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|SHOCK_D3HE_P_YIELD</v>
       </c>
       <c r="C33" s="97" t="s">
         <v>73</v>
@@ -5721,10 +5712,10 @@
       </c>
       <c r="B34" s="97" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|COMPRESSION_D3HEP_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|COMPRESSION_D3HEP_YIELD</v>
       </c>
       <c r="C34" s="97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D34" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5816,10 +5807,10 @@
       </c>
       <c r="B35" s="97" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|RHOR_AT_SHOCK</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|RHOR_AT_SHOCK</v>
       </c>
       <c r="C35" s="97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D35" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5911,10 +5902,10 @@
       </c>
       <c r="B36" s="97" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|RHOR_AT_COMPRESSION</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|RHOR_AT_COMPRESSION</v>
       </c>
       <c r="C36" s="97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D36" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6006,10 +5997,10 @@
       </c>
       <c r="B37" s="97" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|KO_P_TO_NEUTRON_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|KO_P_TO_NEUTRON_RATIO</v>
       </c>
       <c r="C37" s="97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D37" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6101,10 +6092,10 @@
       </c>
       <c r="B38" s="97" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
       </c>
       <c r="C38" s="97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D38" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6196,10 +6187,10 @@
       </c>
       <c r="B39" s="97" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|LOWER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|LOWER_RIGHT|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
       </c>
       <c r="C39" s="97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D39" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6291,7 +6282,7 @@
       </c>
       <c r="B40" s="97" t="str">
         <f t="shared" ref="B40:B46" ca="1" si="22">CONCATENATE(SUBSYSTEM_KEY,"|TC",INDIRECT("Port"),"|",INDIRECT("Instrument"),"|ANALYSIS|CENTER|", C40)</f>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|SHOCK_D3HE_P_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|SHOCK_D3HE_P_YIELD</v>
       </c>
       <c r="C40" s="97" t="s">
         <v>73</v>
@@ -6385,10 +6376,10 @@
       </c>
       <c r="B41" s="97" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|COMPRESSION_D3HEP_YIELD</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|COMPRESSION_D3HEP_YIELD</v>
       </c>
       <c r="C41" s="97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D41" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6479,10 +6470,10 @@
       </c>
       <c r="B42" s="97" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|RHOR_AT_SHOCK</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|RHOR_AT_SHOCK</v>
       </c>
       <c r="C42" s="97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D42" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6573,10 +6564,10 @@
       </c>
       <c r="B43" s="97" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|RHOR_AT_COMPRESSION</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|RHOR_AT_COMPRESSION</v>
       </c>
       <c r="C43" s="97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D43" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6667,10 +6658,10 @@
       </c>
       <c r="B44" s="97" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|KO_P_TO_NEUTRON_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|KO_P_TO_NEUTRON_RATIO</v>
       </c>
       <c r="C44" s="97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D44" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6761,10 +6752,10 @@
       </c>
       <c r="B45" s="97" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|COMPRESSION_ABLATOR_RHOR_FROM_RATIO</v>
       </c>
       <c r="C45" s="97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D45" s="104" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -6855,10 +6846,10 @@
       </c>
       <c r="B46" s="97" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>DESK-TD|TC090-078|WRF|ANALYSIS|CENTER|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
+        <v>DESK-TD|TC|WRF|ANALYSIS|CENTER|COMPRESSION_ABLATOR_RHOR_FROM_KO_P_SPEC</v>
       </c>
       <c r="C46" s="97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D46" s="104" t="str">
         <f ca="1">IF(ISBLANK(OFFSET(INDIRECT(R46), 0, -1, 1, 1)), "", OFFSET(INDIRECT(R46), 0, -1, 1, 1))</f>
@@ -6946,6 +6937,7 @@
       <c r="AA47" s="81"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <sheetProtection password="C595" sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="X46 X35">
     <cfRule type="cellIs" dxfId="2" priority="3" stopIfTrue="1" operator="equal">
